--- a/preprocessing/oversampling.xlsx
+++ b/preprocessing/oversampling.xlsx
@@ -112,7 +112,7 @@
     <t xml:space="preserve">cropped_0001_label_wmLYCo2j_1440_1440.png</t>
   </si>
   <si>
-    <t xml:space="preserve">cropped_00000002_4_480_960.png </t>
+    <t xml:space="preserve">cropped_00000002_4_480_960.png</t>
   </si>
   <si>
     <t xml:space="preserve">cropped_00000002_4_2400_960.png</t>
@@ -166,7 +166,7 @@
     <t xml:space="preserve">cropped_0004_label_1XDZxhBC_0_1440.png</t>
   </si>
   <si>
-    <t xml:space="preserve">cropped_0004_label_5caRcr55_1920_960.png **</t>
+    <t xml:space="preserve">cropped_0004_label_5caRcr55_1920_960.png</t>
   </si>
   <si>
     <t xml:space="preserve">cropped_0004_label_FcjmsocM_960_480.png</t>

--- a/preprocessing/oversampling.xlsx
+++ b/preprocessing/oversampling.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="83">
   <si>
     <t xml:space="preserve">name</t>
   </si>
@@ -179,6 +179,96 @@
   </si>
   <si>
     <t xml:space="preserve">cropped_0004_label_FCjmsocM_2400_480.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cropped_0004_label_FcjmsocM_2880_480.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cropped_0004_label_KhubE3m1_480_1440.png **</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cropped_0005_label_5YuL3VcR_1920_480.png ***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cropped_0005_label_egaPlFje_1440_960.png ***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cropped_0005_label_FcjmsocM_480_480.png  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">cropped_0005_label_FcjmsocM_960_480.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cropped_0005_label_FcjmsocM_2400_480.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cropped_0005_label_FcjmsocM_0_0.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cropped_0005_label_nKTYvVYf_1920_1440.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cropped_0005_label_nKTYvVYf_2400_1440.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cropped_0005_label_zsq5uyoY_1920_960.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cropped_0005_label_zsq5uyoY_960_1440.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cropped_0006_label_5caRcr55_0_480.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cropped_00000007_3_2880_960.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cropped_00000007_3_3360_960.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cropped_00000008_3_1920_960.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cropped_0009_label_BRxm2MyU_1920_480.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cropped_0009_label_ExoBsFee_2880_960.png </t>
+  </si>
+  <si>
+    <t xml:space="preserve">cropped_0009_label_ExoBsFee_1440_1440.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cropped_0009_label_KhubE3m1_1440_0.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cropped_0009_label_KhubE3m1_960_1440.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cropped_0010_label_h2qBCL3Q_2880_960.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cropped_0011_label_ExoBsFee_1920_1440.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cropped_0011_label_lY40XnMe_2400_960.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cropped_00000012_1_3360_960.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cropped_00000012_1_3840_960.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cropped_0012_label_1XDZxhBC_2400_960.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cropped_0012_label_egaPlFje_1440_960.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cropped_0012_label_Y0sRpXgl_1920_960.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cropped_0012_label_Y0sRpXgl_3840_2400.png</t>
   </si>
 </sst>
 </file>
@@ -280,7 +370,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B1048576"/>
+  <dimension ref="A1:B86"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="46.78"/>
@@ -722,7 +812,262 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="55" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B55" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B56" s="0" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B57" s="0" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B58" s="0" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B59" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B60" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B61" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B62" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B63" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B64" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B65" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B66" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B67" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B68" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B69" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B70" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B71" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B72" s="0" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B73" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B74" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B75" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B76" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B77" s="0" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B78" s="0" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B79" s="0" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B80" s="0" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B81" s="0" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B82" s="0" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B83" s="0" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B84" s="0" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B85" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B86" s="0" t="n">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.3"/>

--- a/preprocessing/oversampling.xlsx
+++ b/preprocessing/oversampling.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="82">
   <si>
     <t xml:space="preserve">name</t>
   </si>
@@ -184,13 +184,10 @@
     <t xml:space="preserve">cropped_0004_label_FcjmsocM_2880_480.png</t>
   </si>
   <si>
-    <t xml:space="preserve">cropped_0004_label_KhubE3m1_480_1440.png **</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cropped_0005_label_5YuL3VcR_1920_480.png ***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cropped_0005_label_egaPlFje_1440_960.png ***</t>
+    <t xml:space="preserve">cropped_0004_label_KhubE3m1_480_1440.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cropped_0005_label_5YuL3VcR_1920_480.png</t>
   </si>
   <si>
     <t xml:space="preserve">cropped_0005_label_FcjmsocM_480_480.png  </t>
@@ -838,7 +835,7 @@
     </row>
     <row r="58" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="1" t="s">
-        <v>56</v>
+        <v>7</v>
       </c>
       <c r="B58" s="0" t="n">
         <v>3</v>
@@ -846,7 +843,7 @@
     </row>
     <row r="59" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B59" s="0" t="n">
         <v>1</v>
@@ -854,7 +851,7 @@
     </row>
     <row r="60" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B60" s="0" t="n">
         <v>1</v>
@@ -862,7 +859,7 @@
     </row>
     <row r="61" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B61" s="0" t="n">
         <v>1</v>
@@ -870,7 +867,7 @@
     </row>
     <row r="62" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B62" s="0" t="n">
         <v>1</v>
@@ -878,7 +875,7 @@
     </row>
     <row r="63" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B63" s="0" t="n">
         <v>1</v>
@@ -886,7 +883,7 @@
     </row>
     <row r="64" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B64" s="0" t="n">
         <v>1</v>
@@ -894,7 +891,7 @@
     </row>
     <row r="65" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B65" s="0" t="n">
         <v>1</v>
@@ -902,7 +899,7 @@
     </row>
     <row r="66" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B66" s="0" t="n">
         <v>1</v>
@@ -910,7 +907,7 @@
     </row>
     <row r="67" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B67" s="0" t="n">
         <v>1</v>
@@ -918,7 +915,7 @@
     </row>
     <row r="68" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B68" s="0" t="n">
         <v>1</v>
@@ -926,7 +923,7 @@
     </row>
     <row r="69" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B69" s="0" t="n">
         <v>1</v>
@@ -934,7 +931,7 @@
     </row>
     <row r="70" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B70" s="0" t="n">
         <v>1</v>
@@ -942,7 +939,7 @@
     </row>
     <row r="71" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B71" s="0" t="n">
         <v>1</v>
@@ -950,7 +947,7 @@
     </row>
     <row r="72" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B72" s="0" t="n">
         <v>3</v>
@@ -958,7 +955,7 @@
     </row>
     <row r="73" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B73" s="0" t="n">
         <v>1</v>
@@ -966,7 +963,7 @@
     </row>
     <row r="74" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B74" s="0" t="n">
         <v>1</v>
@@ -974,7 +971,7 @@
     </row>
     <row r="75" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B75" s="0" t="n">
         <v>1</v>
@@ -982,7 +979,7 @@
     </row>
     <row r="76" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B76" s="0" t="n">
         <v>1</v>
@@ -990,15 +987,15 @@
     </row>
     <row r="77" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B77" s="0" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B78" s="0" t="n">
         <v>3</v>
@@ -1009,7 +1006,7 @@
         <v>24</v>
       </c>
       <c r="B79" s="0" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1022,7 +1019,7 @@
     </row>
     <row r="81" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B81" s="0" t="n">
         <v>2</v>
@@ -1030,7 +1027,7 @@
     </row>
     <row r="82" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B82" s="0" t="n">
         <v>2</v>
@@ -1038,7 +1035,7 @@
     </row>
     <row r="83" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B83" s="0" t="n">
         <v>2</v>
@@ -1046,7 +1043,7 @@
     </row>
     <row r="84" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B84" s="0" t="n">
         <v>2</v>
@@ -1054,7 +1051,7 @@
     </row>
     <row r="85" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B85" s="0" t="n">
         <v>1</v>
@@ -1062,7 +1059,7 @@
     </row>
     <row r="86" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B86" s="0" t="n">
         <v>2</v>
